--- a/Excel/FashionSuitConfig.xlsx
+++ b/Excel/FashionSuitConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="12990" windowHeight="10290"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -56,7 +56,7 @@
     <t>string</t>
   </si>
   <si>
-    <t>战神之力</t>
+    <t>斩仙之力</t>
   </si>
   <si>
     <t>2004</t>
@@ -68,25 +68,25 @@
     <t>2</t>
   </si>
   <si>
-    <t>恶魔之力</t>
+    <t>魔尊之力</t>
   </si>
   <si>
     <t>2005</t>
   </si>
   <si>
-    <t>幽灵之力</t>
+    <t>幽冥之力</t>
   </si>
   <si>
     <t>2006</t>
   </si>
   <si>
-    <t>圣战之力</t>
+    <t>战魂之力</t>
   </si>
   <si>
     <t>2002</t>
   </si>
   <si>
-    <t>法神之力</t>
+    <t>法魂之力</t>
   </si>
   <si>
     <t>2001</t>
@@ -98,7 +98,7 @@
     <t>1</t>
   </si>
   <si>
-    <t>天尊之力</t>
+    <t>道魂之力</t>
   </si>
   <si>
     <t>2003</t>
@@ -1284,7 +1284,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="D3 E3 F3 G3 D4 E4 F4 G4 D5 E5:G5 C3:C5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="D3:G3 C3:C5 D4:G5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/FashionSuitConfig.xlsx
+++ b/Excel/FashionSuitConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="12990" windowHeight="10290"/>
+    <workbookView windowWidth="27952" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="32">
   <si>
     <t>ID</t>
   </si>
@@ -35,13 +35,13 @@
     <t>Name</t>
   </si>
   <si>
-    <t>AttrId</t>
-  </si>
-  <si>
-    <t>AttrValue</t>
-  </si>
-  <si>
-    <t>AttrRise</t>
+    <t>AttrIdList</t>
+  </si>
+  <si>
+    <t>AttrValueList</t>
+  </si>
+  <si>
+    <t>AttrRiseList</t>
   </si>
   <si>
     <t>MaxLevel</t>
@@ -108,6 +108,21 @@
   </si>
   <si>
     <t>3</t>
+  </si>
+  <si>
+    <t>天神之力</t>
+  </si>
+  <si>
+    <t>2001,2002,2003</t>
+  </si>
+  <si>
+    <t>2,4,6</t>
+  </si>
+  <si>
+    <t>魔神之力</t>
+  </si>
+  <si>
+    <t>3,6,9</t>
   </si>
 </sst>
 </file>
@@ -1067,17 +1082,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
+    <col min="1" max="1" width="6.87610619469027" style="2" customWidth="1"/>
     <col min="2" max="2" width="9" style="2"/>
-    <col min="3" max="3" width="9.875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="12.125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.87610619469027" style="1" customWidth="1"/>
+    <col min="4" max="4" width="12.1238938053097" style="1" customWidth="1"/>
     <col min="5" max="5" width="13" style="2" customWidth="1"/>
-    <col min="6" max="6" width="10.125" style="2" customWidth="1"/>
-    <col min="7" max="7" width="12.25" style="2" customWidth="1"/>
-    <col min="8" max="8" width="12.25" style="1" customWidth="1"/>
+    <col min="6" max="6" width="10.1238938053097" style="2" customWidth="1"/>
+    <col min="7" max="7" width="12.2477876106195" style="2" customWidth="1"/>
+    <col min="8" max="8" width="12.2477876106195" style="1" customWidth="1"/>
     <col min="9" max="16368" width="9" style="2"/>
     <col min="16369" max="16384" width="9" style="1"/>
   </cols>
@@ -1282,9 +1297,49 @@
         <v>20</v>
       </c>
     </row>
+    <row r="12" customHeight="1" spans="3:8">
+      <c r="C12" s="1">
+        <v>7</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H12" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="3:8">
+      <c r="C13" s="1">
+        <v>8</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H13" s="1">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="D3:G3 C3:C5 D4:G5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C5:G5 C3:G4" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/FashionSuitConfig.xlsx
+++ b/Excel/FashionSuitConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="33">
   <si>
     <t>ID</t>
   </si>
@@ -54,6 +54,9 @@
   </si>
   <si>
     <t>string</t>
+  </si>
+  <si>
+    <t>int[]</t>
   </si>
   <si>
     <t>斩仙之力</t>
@@ -1165,13 +1168,13 @@
         <v>8</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>7</v>
@@ -1182,16 +1185,16 @@
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H6" s="1">
         <v>20</v>
@@ -1202,16 +1205,16 @@
         <v>2</v>
       </c>
       <c r="D7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" s="4" t="s">
         <v>13</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>12</v>
       </c>
       <c r="H7" s="1">
         <v>20</v>
@@ -1222,16 +1225,16 @@
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H8" s="1">
         <v>20</v>
@@ -1242,16 +1245,16 @@
         <v>4</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H9" s="1">
         <v>20</v>
@@ -1262,16 +1265,16 @@
         <v>5</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H10" s="1">
         <v>20</v>
@@ -1282,16 +1285,16 @@
         <v>6</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H11" s="1">
         <v>20</v>
@@ -1302,16 +1305,16 @@
         <v>7</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H12" s="1">
         <v>20</v>
@@ -1322,16 +1325,16 @@
         <v>8</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H13" s="1">
         <v>20</v>
@@ -1339,7 +1342,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C5:G5 C3:G4" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C5:D5 E5 F5 G5 C3:G4" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/FashionSuitConfig.xlsx
+++ b/Excel/FashionSuitConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="34">
   <si>
     <t>ID</t>
   </si>
@@ -116,16 +116,19 @@
     <t>天神之力</t>
   </si>
   <si>
-    <t>2001,2002,2003</t>
-  </si>
-  <si>
-    <t>2,4,6</t>
+    <t>2004,2005,2006,2003</t>
+  </si>
+  <si>
+    <t>2,2,2,4</t>
   </si>
   <si>
     <t>魔神之力</t>
   </si>
   <si>
-    <t>3,6,9</t>
+    <t>2001,2002,2003,2010</t>
+  </si>
+  <si>
+    <t>2,4,6,2</t>
   </si>
 </sst>
 </file>
@@ -1092,7 +1095,7 @@
     <col min="2" max="2" width="9" style="2"/>
     <col min="3" max="3" width="9.87610619469027" style="1" customWidth="1"/>
     <col min="4" max="4" width="12.1238938053097" style="1" customWidth="1"/>
-    <col min="5" max="5" width="13" style="2" customWidth="1"/>
+    <col min="5" max="5" width="22.6371681415929" style="2" customWidth="1"/>
     <col min="6" max="6" width="10.1238938053097" style="2" customWidth="1"/>
     <col min="7" max="7" width="12.2477876106195" style="2" customWidth="1"/>
     <col min="8" max="8" width="12.2477876106195" style="1" customWidth="1"/>
@@ -1328,13 +1331,13 @@
         <v>31</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H13" s="1">
         <v>20</v>
@@ -1342,7 +1345,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C5:D5 E5 F5 G5 C3:G4" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:G5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/FashionSuitConfig.xlsx
+++ b/Excel/FashionSuitConfig.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27952" windowHeight="12255"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="40">
   <si>
     <t>ID</t>
   </si>
@@ -129,6 +129,24 @@
   </si>
   <si>
     <t>2,4,6,2</t>
+  </si>
+  <si>
+    <t>仙神之力</t>
+  </si>
+  <si>
+    <t>2001,2003,2012,2010</t>
+  </si>
+  <si>
+    <t>2,4,4,2</t>
+  </si>
+  <si>
+    <t>邪神之力</t>
+  </si>
+  <si>
+    <t>2001,2003,2010,2013</t>
+  </si>
+  <si>
+    <t>2,4,2,2</t>
   </si>
 </sst>
 </file>
@@ -1088,29 +1106,29 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="6.87610619469027" style="2" customWidth="1"/>
+    <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
     <col min="2" max="2" width="9" style="2"/>
-    <col min="3" max="3" width="9.87610619469027" style="1" customWidth="1"/>
-    <col min="4" max="4" width="12.1238938053097" style="1" customWidth="1"/>
-    <col min="5" max="5" width="22.6371681415929" style="2" customWidth="1"/>
-    <col min="6" max="6" width="10.1238938053097" style="2" customWidth="1"/>
-    <col min="7" max="7" width="12.2477876106195" style="2" customWidth="1"/>
-    <col min="8" max="8" width="12.2477876106195" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="12.125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="22.6333333333333" style="2" customWidth="1"/>
+    <col min="6" max="6" width="10.125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="12.25" style="2" customWidth="1"/>
+    <col min="8" max="8" width="12.25" style="1" customWidth="1"/>
     <col min="9" max="16368" width="9" style="2"/>
     <col min="16369" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:7">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:8">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
     </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:7">
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:8">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="E2" s="2"/>
@@ -1183,7 +1201,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:8">
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:8">
       <c r="C6" s="1">
         <v>1</v>
       </c>
@@ -1203,7 +1221,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:8">
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="1:8">
       <c r="C7" s="1">
         <v>2</v>
       </c>
@@ -1223,7 +1241,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:8">
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="1:8">
       <c r="C8" s="1">
         <v>3</v>
       </c>
@@ -1243,7 +1261,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:8">
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="1:8">
       <c r="C9" s="1">
         <v>4</v>
       </c>
@@ -1263,7 +1281,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:8">
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="1:8">
       <c r="C10" s="1">
         <v>5</v>
       </c>
@@ -1283,7 +1301,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:8">
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="1:8">
       <c r="C11" s="1">
         <v>6</v>
       </c>
@@ -1303,7 +1321,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" customHeight="1" spans="3:8">
+    <row r="12" customHeight="1" spans="1:8">
       <c r="C12" s="1">
         <v>7</v>
       </c>
@@ -1323,7 +1341,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" customHeight="1" spans="3:8">
+    <row r="13" customHeight="1" spans="1:8">
       <c r="C13" s="1">
         <v>8</v>
       </c>
@@ -1340,6 +1358,46 @@
         <v>33</v>
       </c>
       <c r="H13" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="1:8">
+      <c r="C14" s="1">
+        <v>9</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="H14" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="1:8">
+      <c r="C15" s="1">
+        <v>10</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="H15" s="1">
         <v>20</v>
       </c>
     </row>
